--- a/docs/data_dictionary.xlsx
+++ b/docs/data_dictionary.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Must be present. A repeated txn_id is quarantined as a duplicate.</t>
+          <t>Must be present, at most 32 characters, no control characters. A repeated txn_id is quarantined as a duplicate.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Accepts YYYY-MM-DD, MM/DD/YYYY, DD-Mon-YYYY, YYYY/MM/DD. Anything else is quarantined.</t>
+          <t>Accepts YYYY-MM-DD, MM/DD/YYYY (month first), DD-Mon-YYYY, YYYY/MM/DD; year 2000 to 2099. Anything else is quarantined.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Exactly 4 digits. A card with no matching cardholder in employees.json is quarantined.</t>
+          <t>Exactly 4 ASCII digits. A card with no matching cardholder in employees.json is quarantined.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Must be present (1-120 characters). A blank merchant is quarantined.</t>
+          <t>Must be present (1-120 characters), no control characters. A blank merchant is quarantined.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Exactly 4 digits. Codes not in policy_rules.json fall back to Miscellaneous.</t>
+          <t>Exactly 4 ASCII digits. Codes not in policy_rules.json fall back to Miscellaneous.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Accepts $ and thousands commas. Max 2 decimals, absolute value up to $1,000,000. Non-numeric (e.g. N/A) is quarantined.</t>
+          <t>US format only: $ and correctly placed thousands commas (1,234.50). 1,23 or 12 34 are rejected, never guessed. Max 2 decimals, up to $1,000,000. ASCII digits only.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>None. Blank is allowed.</t>
+          <t>Optional, at most 500 characters. Tabs and line breaks become spaces; other control characters quarantine the row.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
